--- a/Accounting-Analytics-Textbook/Unit 1/data/Employee credit card purchases.xlsx
+++ b/Accounting-Analytics-Textbook/Unit 1/data/Employee credit card purchases.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/f27c7dfe41a57d57/Texas State/ACC 3323/Lecture slides/By Topic/Unit 1 - Process of Analytics/1-01 Process of Analytics/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://txst-my.sharepoint.com/personal/mih53_txstate_edu/Documents/ACC 3323/Lecture slides/By Topic/Unit 1 - Process of Analytics/1-2 Process of Analytics/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{1250B9B6-63AF-48E1-B929-FA077022E070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DE18205B-9056-4522-AA6F-6F8B5ECA4FD9}"/>
+  <xr:revisionPtr revIDLastSave="58" documentId="8_{1250B9B6-63AF-48E1-B929-FA077022E070}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4F0B93F9-A28B-4C4B-B198-98E095AF9D39}"/>
   <bookViews>
-    <workbookView xWindow="25305" yWindow="105" windowWidth="22215" windowHeight="17280" xr2:uid="{51346E83-5DF8-4BA9-9D58-17E5E7C87675}"/>
+    <workbookView xWindow="38190" yWindow="0" windowWidth="19410" windowHeight="17280" xr2:uid="{51346E83-5DF8-4BA9-9D58-17E5E7C87675}"/>
   </bookViews>
   <sheets>
     <sheet name="P-Card Subset" sheetId="3" r:id="rId1"/>
@@ -38,19 +38,10 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="54" uniqueCount="32">
   <si>
-    <t>ItemDescription</t>
-  </si>
-  <si>
     <t>Amount</t>
   </si>
   <si>
     <t>Vendor</t>
-  </si>
-  <si>
-    <t>TransactionDate</t>
-  </si>
-  <si>
-    <t>MerchantCategoryCode</t>
   </si>
   <si>
     <t>GENERAL PURCHASE</t>
@@ -133,6 +124,15 @@
   <si>
     <t>SABRENT MULTI-Dsply USB 2 PCE
 CTG Ultima SVGA Mon</t>
+  </si>
+  <si>
+    <t>Transaction Date</t>
+  </si>
+  <si>
+    <t>Vendor Category Code</t>
+  </si>
+  <si>
+    <t>Item Description</t>
   </si>
 </sst>
 </file>
@@ -171,10 +171,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
@@ -187,16 +185,36 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
+  <dxfs count="7">
     <dxf>
       <numFmt numFmtId="34" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <numFmt numFmtId="19" formatCode="m/d/yyyy"/>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <alignment horizontal="general" vertical="top" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -212,7 +230,7 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F41FBD48-32FA-4A03-A3F2-03AFD8815C8F}" name="Table1" displayName="Table1" ref="A1:F13" totalsRowShown="0">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{F41FBD48-32FA-4A03-A3F2-03AFD8815C8F}" name="Table1" displayName="Table1" ref="A1:F13" totalsRowShown="0" dataDxfId="6">
   <autoFilter ref="A1:F13" xr:uid="{F41FBD48-32FA-4A03-A3F2-03AFD8815C8F}">
     <filterColumn colId="0" hiddenButton="1"/>
     <filterColumn colId="1" hiddenButton="1"/>
@@ -222,11 +240,11 @@
     <filterColumn colId="5" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="6">
-    <tableColumn id="1" xr3:uid="{8E70E755-7CC9-4A91-B0DB-612EDFC5F55F}" name="TransactionDate" dataDxfId="1"/>
-    <tableColumn id="2" xr3:uid="{D3268F33-B310-4B5C-83A8-B80C0259029F}" name="Name"/>
-    <tableColumn id="3" xr3:uid="{2183ED87-4096-49BA-B688-6CAF944E1122}" name="ItemDescription"/>
-    <tableColumn id="4" xr3:uid="{B2C1836D-7914-414E-AACF-84FF420B5B23}" name="Vendor"/>
-    <tableColumn id="5" xr3:uid="{D10067DA-AEAB-4C20-B490-22EDC0CA012D}" name="MerchantCategoryCode"/>
+    <tableColumn id="1" xr3:uid="{8E70E755-7CC9-4A91-B0DB-612EDFC5F55F}" name="Transaction Date" dataDxfId="5"/>
+    <tableColumn id="2" xr3:uid="{D3268F33-B310-4B5C-83A8-B80C0259029F}" name="Name" dataDxfId="4"/>
+    <tableColumn id="3" xr3:uid="{2183ED87-4096-49BA-B688-6CAF944E1122}" name="Item Description" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{B2C1836D-7914-414E-AACF-84FF420B5B23}" name="Vendor" dataDxfId="2"/>
+    <tableColumn id="5" xr3:uid="{D10067DA-AEAB-4C20-B490-22EDC0CA012D}" name="Vendor Category Code" dataDxfId="1"/>
     <tableColumn id="6" xr3:uid="{AD23A729-9012-4DBE-9C82-47E942BEC30B}" name="Amount" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium16" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
@@ -536,51 +554,51 @@
   <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="15.42578125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.5703125" customWidth="1"/>
     <col min="2" max="2" width="10.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="29.7109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="60.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.85546875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="44.85546875" customWidth="1"/>
     <col min="6" max="6" width="10.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>3</v>
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>29</v>
       </c>
       <c r="B1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C1" t="s">
+        <v>31</v>
+      </c>
+      <c r="D1" t="s">
+        <v>1</v>
+      </c>
+      <c r="E1" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="C1" t="s">
+      <c r="F1" t="s">
         <v>0</v>
       </c>
-      <c r="D1" t="s">
-        <v>2</v>
-      </c>
-      <c r="E1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    </row>
+    <row r="2" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>41976</v>
       </c>
-      <c r="B2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="2">
+      <c r="B2" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E2" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="F2" s="4">
         <v>3659.84</v>
       </c>
     </row>
@@ -588,59 +606,59 @@
       <c r="A3" s="1">
         <v>41673</v>
       </c>
-      <c r="B3" t="s">
-        <v>29</v>
-      </c>
-      <c r="C3" t="s">
-        <v>5</v>
-      </c>
-      <c r="D3" t="s">
-        <v>25</v>
-      </c>
-      <c r="E3" t="s">
-        <v>7</v>
-      </c>
-      <c r="F3" s="2">
+      <c r="B3" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E3" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F3" s="4">
         <v>1061.27</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>41991</v>
       </c>
-      <c r="B4" t="s">
-        <v>28</v>
-      </c>
-      <c r="C4" t="s">
-        <v>5</v>
-      </c>
-      <c r="D4" t="s">
-        <v>23</v>
-      </c>
-      <c r="E4" t="s">
-        <v>13</v>
-      </c>
-      <c r="F4" s="2">
+      <c r="B4" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E4" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="F4" s="4">
         <v>516.86</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>41983</v>
       </c>
-      <c r="B5" t="s">
-        <v>28</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="B5" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="D5" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" t="s">
-        <v>8</v>
-      </c>
-      <c r="F5" s="2">
+      <c r="F5" s="4">
         <v>297.72000000000003</v>
       </c>
     </row>
@@ -648,19 +666,19 @@
       <c r="A6" s="1">
         <v>41659</v>
       </c>
-      <c r="B6" t="s">
-        <v>29</v>
-      </c>
-      <c r="C6" t="s">
-        <v>5</v>
-      </c>
-      <c r="D6" t="s">
-        <v>21</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="B6" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="3" t="s">
+        <v>4</v>
+      </c>
+      <c r="F6" s="4">
         <v>270</v>
       </c>
     </row>
@@ -668,19 +686,19 @@
       <c r="A7" s="1">
         <v>41675</v>
       </c>
-      <c r="B7" t="s">
-        <v>29</v>
-      </c>
-      <c r="C7" t="s">
-        <v>5</v>
-      </c>
-      <c r="D7" t="s">
-        <v>24</v>
-      </c>
-      <c r="E7" t="s">
-        <v>18</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="B7" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E7" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="F7" s="4">
         <v>259</v>
       </c>
     </row>
@@ -688,59 +706,59 @@
       <c r="A8" s="1">
         <v>41711</v>
       </c>
-      <c r="B8" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" t="s">
-        <v>5</v>
-      </c>
-      <c r="D8" t="s">
-        <v>11</v>
-      </c>
-      <c r="E8" t="s">
-        <v>12</v>
-      </c>
-      <c r="F8" s="2">
+      <c r="B8" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F8" s="4">
         <v>256.63</v>
       </c>
     </row>
-    <row r="9" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A9" s="3">
+    <row r="9" spans="1:6" ht="60" x14ac:dyDescent="0.25">
+      <c r="A9" s="1">
         <v>41667</v>
       </c>
-      <c r="B9" s="4" t="s">
-        <v>29</v>
-      </c>
-      <c r="C9" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="F9" s="6">
+      <c r="B9" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="F9" s="4">
         <v>107.25</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>41974</v>
       </c>
-      <c r="B10" t="s">
-        <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>5</v>
-      </c>
-      <c r="D10" t="s">
-        <v>14</v>
-      </c>
-      <c r="E10" t="s">
-        <v>15</v>
-      </c>
-      <c r="F10" s="2">
+      <c r="B10" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="F10" s="4">
         <v>63.79</v>
       </c>
     </row>
@@ -748,19 +766,19 @@
       <c r="A11" s="1">
         <v>41712</v>
       </c>
-      <c r="B11" t="s">
-        <v>27</v>
-      </c>
-      <c r="C11" t="s">
-        <v>5</v>
-      </c>
-      <c r="D11" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" t="s">
-        <v>12</v>
-      </c>
-      <c r="F11" s="2">
+      <c r="B11" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C11" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="F11" s="4">
         <v>35.78</v>
       </c>
     </row>
@@ -768,19 +786,19 @@
       <c r="A12" s="1">
         <v>41718</v>
       </c>
-      <c r="B12" t="s">
-        <v>27</v>
-      </c>
-      <c r="C12" t="s">
-        <v>5</v>
-      </c>
-      <c r="D12" t="s">
-        <v>9</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" s="2">
+      <c r="B12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="C12" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="F12" s="4">
         <v>9.9700000000000006</v>
       </c>
     </row>
@@ -788,19 +806,19 @@
       <c r="A13" s="1">
         <v>41675</v>
       </c>
-      <c r="B13" t="s">
-        <v>29</v>
-      </c>
-      <c r="C13" t="s">
-        <v>5</v>
-      </c>
-      <c r="D13" t="s">
+      <c r="B13" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E13" t="s">
-        <v>6</v>
-      </c>
-      <c r="F13" s="2">
+      <c r="C13" s="2" t="s">
+        <v>2</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="F13" s="4">
         <v>0.99</v>
       </c>
     </row>
@@ -808,8 +826,9 @@
   <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:F13">
     <sortCondition descending="1" ref="F2:F13"/>
   </sortState>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup scale="78" orientation="landscape" r:id="rId1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="1" right="1" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup scale="94" orientation="landscape" r:id="rId1"/>
   <headerFooter>
     <oddHeader>&amp;C&amp;"-,Bold"&amp;18Employee Credit Card Purchases</oddHeader>
   </headerFooter>
